--- a/artfynd/A 7832-2025 artfynd.xlsx
+++ b/artfynd/A 7832-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122508709</v>
+        <v>122508561</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581196</v>
+        <v>581217</v>
       </c>
       <c r="R2" t="n">
-        <v>6418384</v>
+        <v>6418390</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122510520</v>
+        <v>122510457</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581270</v>
+        <v>581311</v>
       </c>
       <c r="R3" t="n">
-        <v>6418180</v>
+        <v>6418384</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122508687</v>
+        <v>122508709</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>581196</v>
       </c>
       <c r="R4" t="n">
-        <v>6418358</v>
+        <v>6418384</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122508528</v>
+        <v>122508578</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581231</v>
+        <v>581224</v>
       </c>
       <c r="R5" t="n">
-        <v>6418384</v>
+        <v>6418372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122508561</v>
+        <v>122508654</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581217</v>
+        <v>581242</v>
       </c>
       <c r="R6" t="n">
-        <v>6418390</v>
+        <v>6418411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122508679</v>
+        <v>122510535</v>
       </c>
       <c r="B7" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,7 +1263,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1278,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581209</v>
+        <v>581276</v>
       </c>
       <c r="R7" t="n">
-        <v>6418354</v>
+        <v>6418168</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122508509</v>
+        <v>122508619</v>
       </c>
       <c r="B8" t="n">
-        <v>57753</v>
+        <v>98241</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,39 +1357,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581279</v>
+        <v>581220</v>
       </c>
       <c r="R8" t="n">
-        <v>6418360</v>
+        <v>6418393</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,6 +1437,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122510543</v>
+        <v>122508745</v>
       </c>
       <c r="B9" t="n">
-        <v>57536</v>
+        <v>98241</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,39 +1468,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581276</v>
+        <v>581213</v>
       </c>
       <c r="R9" t="n">
-        <v>6418168</v>
+        <v>6418385</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,6 +1548,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1569,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122508717</v>
+        <v>122510520</v>
       </c>
       <c r="B10" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581193</v>
+        <v>581270</v>
       </c>
       <c r="R10" t="n">
-        <v>6418402</v>
+        <v>6418180</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122508664</v>
+        <v>122508679</v>
       </c>
       <c r="B11" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581212</v>
+        <v>581209</v>
       </c>
       <c r="R11" t="n">
-        <v>6418357</v>
+        <v>6418354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122510530</v>
+        <v>122508596</v>
       </c>
       <c r="B12" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581277</v>
+        <v>581225</v>
       </c>
       <c r="R12" t="n">
-        <v>6418181</v>
+        <v>6418386</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122510457</v>
+        <v>122508528</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,7 +1948,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581311</v>
+        <v>581231</v>
       </c>
       <c r="R13" t="n">
         <v>6418384</v>
@@ -2013,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122510535</v>
+        <v>122510446</v>
       </c>
       <c r="B14" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,11 +2044,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2065,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581276</v>
+        <v>581296</v>
       </c>
       <c r="R14" t="n">
-        <v>6418168</v>
+        <v>6418371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122508745</v>
+        <v>122508626</v>
       </c>
       <c r="B15" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581213</v>
+        <v>581228</v>
       </c>
       <c r="R15" t="n">
-        <v>6418385</v>
+        <v>6418409</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,10 +2233,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122508619</v>
+        <v>122510543</v>
       </c>
       <c r="B16" t="n">
-        <v>98240</v>
+        <v>57537</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2251,35 +2245,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2287,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581220</v>
+        <v>581276</v>
       </c>
       <c r="R16" t="n">
-        <v>6418393</v>
+        <v>6418168</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2329,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2350,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122508654</v>
+        <v>122508664</v>
       </c>
       <c r="B17" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581242</v>
+        <v>581212</v>
       </c>
       <c r="R17" t="n">
-        <v>6418411</v>
+        <v>6418357</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122508626</v>
+        <v>122508687</v>
       </c>
       <c r="B18" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581228</v>
+        <v>581196</v>
       </c>
       <c r="R18" t="n">
-        <v>6418409</v>
+        <v>6418358</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2572,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122510446</v>
+        <v>122510530</v>
       </c>
       <c r="B19" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,10 +2617,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581296</v>
+        <v>581277</v>
       </c>
       <c r="R19" t="n">
-        <v>6418371</v>
+        <v>6418181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2686,7 +2683,7 @@
         <v>122508731</v>
       </c>
       <c r="B20" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2794,10 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122508596</v>
+        <v>122508509</v>
       </c>
       <c r="B21" t="n">
-        <v>98240</v>
+        <v>57754</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2806,35 +2803,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2842,13 +2843,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581225</v>
+        <v>581279</v>
       </c>
       <c r="R21" t="n">
-        <v>6418386</v>
+        <v>6418360</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2886,7 +2887,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2905,10 +2905,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122508578</v>
+        <v>122510475</v>
       </c>
       <c r="B22" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581224</v>
+        <v>581315</v>
       </c>
       <c r="R22" t="n">
-        <v>6418372</v>
+        <v>6418387</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122510475</v>
+        <v>122508717</v>
       </c>
       <c r="B23" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581315</v>
+        <v>581193</v>
       </c>
       <c r="R23" t="n">
-        <v>6418387</v>
+        <v>6418402</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 7832-2025 artfynd.xlsx
+++ b/artfynd/A 7832-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122508561</v>
+        <v>122508596</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581217</v>
+        <v>581225</v>
       </c>
       <c r="R2" t="n">
-        <v>6418390</v>
+        <v>6418386</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122510457</v>
+        <v>122508509</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>57754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581311</v>
+        <v>581279</v>
       </c>
       <c r="R3" t="n">
-        <v>6418384</v>
+        <v>6418360</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122508709</v>
+        <v>122510530</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581196</v>
+        <v>581277</v>
       </c>
       <c r="R4" t="n">
-        <v>6418384</v>
+        <v>6418181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122508578</v>
+        <v>122510446</v>
       </c>
       <c r="B5" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581224</v>
+        <v>581296</v>
       </c>
       <c r="R5" t="n">
-        <v>6418372</v>
+        <v>6418371</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122508654</v>
+        <v>122510520</v>
       </c>
       <c r="B6" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581242</v>
+        <v>581270</v>
       </c>
       <c r="R6" t="n">
-        <v>6418411</v>
+        <v>6418180</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122510535</v>
+        <v>122508619</v>
       </c>
       <c r="B7" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,11 +1266,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1282,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581276</v>
+        <v>581220</v>
       </c>
       <c r="R7" t="n">
-        <v>6418168</v>
+        <v>6418393</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122508619</v>
+        <v>122508626</v>
       </c>
       <c r="B8" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581220</v>
+        <v>581228</v>
       </c>
       <c r="R8" t="n">
-        <v>6418393</v>
+        <v>6418409</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122508745</v>
+        <v>122508679</v>
       </c>
       <c r="B9" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581213</v>
+        <v>581209</v>
       </c>
       <c r="R9" t="n">
-        <v>6418385</v>
+        <v>6418354</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122510520</v>
+        <v>122508578</v>
       </c>
       <c r="B10" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581270</v>
+        <v>581224</v>
       </c>
       <c r="R10" t="n">
-        <v>6418180</v>
+        <v>6418372</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122508679</v>
+        <v>122510535</v>
       </c>
       <c r="B11" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,7 +1710,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1726,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581209</v>
+        <v>581276</v>
       </c>
       <c r="R11" t="n">
-        <v>6418354</v>
+        <v>6418168</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122508596</v>
+        <v>122510475</v>
       </c>
       <c r="B12" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581225</v>
+        <v>581315</v>
       </c>
       <c r="R12" t="n">
-        <v>6418386</v>
+        <v>6418387</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122508528</v>
+        <v>122510543</v>
       </c>
       <c r="B13" t="n">
-        <v>98241</v>
+        <v>57537</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,35 +1915,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1948,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581231</v>
+        <v>581276</v>
       </c>
       <c r="R13" t="n">
-        <v>6418384</v>
+        <v>6418168</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,7 +1999,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2011,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122510446</v>
+        <v>122510457</v>
       </c>
       <c r="B14" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581296</v>
+        <v>581311</v>
       </c>
       <c r="R14" t="n">
-        <v>6418371</v>
+        <v>6418384</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,10 +2128,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122508626</v>
+        <v>122508687</v>
       </c>
       <c r="B15" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581228</v>
+        <v>581196</v>
       </c>
       <c r="R15" t="n">
-        <v>6418409</v>
+        <v>6418358</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122510543</v>
+        <v>122508731</v>
       </c>
       <c r="B16" t="n">
-        <v>57537</v>
+        <v>98244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,39 +2251,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2285,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581276</v>
+        <v>581212</v>
       </c>
       <c r="R16" t="n">
-        <v>6418168</v>
+        <v>6418405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,6 +2331,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2347,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122508664</v>
+        <v>122508709</v>
       </c>
       <c r="B17" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,10 +2398,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581212</v>
+        <v>581196</v>
       </c>
       <c r="R17" t="n">
-        <v>6418357</v>
+        <v>6418384</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,10 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122508687</v>
+        <v>122508745</v>
       </c>
       <c r="B18" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2506,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581196</v>
+        <v>581213</v>
       </c>
       <c r="R18" t="n">
-        <v>6418358</v>
+        <v>6418385</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2569,10 +2572,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122510530</v>
+        <v>122508664</v>
       </c>
       <c r="B19" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581277</v>
+        <v>581212</v>
       </c>
       <c r="R19" t="n">
-        <v>6418181</v>
+        <v>6418357</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2680,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122508731</v>
+        <v>122508528</v>
       </c>
       <c r="B20" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2728,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581212</v>
+        <v>581231</v>
       </c>
       <c r="R20" t="n">
-        <v>6418405</v>
+        <v>6418384</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,10 +2794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122508509</v>
+        <v>122508561</v>
       </c>
       <c r="B21" t="n">
-        <v>57754</v>
+        <v>98244</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2803,39 +2806,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2843,13 +2842,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581279</v>
+        <v>581217</v>
       </c>
       <c r="R21" t="n">
-        <v>6418360</v>
+        <v>6418390</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2887,6 +2886,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2905,10 +2905,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122510475</v>
+        <v>122508717</v>
       </c>
       <c r="B22" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581315</v>
+        <v>581193</v>
       </c>
       <c r="R22" t="n">
-        <v>6418387</v>
+        <v>6418402</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122508717</v>
+        <v>122508654</v>
       </c>
       <c r="B23" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581193</v>
+        <v>581242</v>
       </c>
       <c r="R23" t="n">
-        <v>6418402</v>
+        <v>6418411</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 7832-2025 artfynd.xlsx
+++ b/artfynd/A 7832-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122508596</v>
+        <v>122508679</v>
       </c>
       <c r="B2" t="n">
         <v>98244</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581225</v>
+        <v>581209</v>
       </c>
       <c r="R2" t="n">
-        <v>6418386</v>
+        <v>6418354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122508509</v>
+        <v>122508664</v>
       </c>
       <c r="B3" t="n">
-        <v>57754</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581279</v>
+        <v>581212</v>
       </c>
       <c r="R3" t="n">
-        <v>6418360</v>
+        <v>6418357</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122510530</v>
+        <v>122508717</v>
       </c>
       <c r="B4" t="n">
         <v>98244</v>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581277</v>
+        <v>581193</v>
       </c>
       <c r="R4" t="n">
-        <v>6418181</v>
+        <v>6418402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122510446</v>
+        <v>122508596</v>
       </c>
       <c r="B5" t="n">
         <v>98244</v>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581296</v>
+        <v>581225</v>
       </c>
       <c r="R5" t="n">
-        <v>6418371</v>
+        <v>6418386</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122510520</v>
+        <v>122510457</v>
       </c>
       <c r="B6" t="n">
         <v>98244</v>
@@ -1170,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581270</v>
+        <v>581311</v>
       </c>
       <c r="R6" t="n">
-        <v>6418180</v>
+        <v>6418384</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122508619</v>
+        <v>122510530</v>
       </c>
       <c r="B7" t="n">
         <v>98244</v>
@@ -1281,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581220</v>
+        <v>581277</v>
       </c>
       <c r="R7" t="n">
-        <v>6418393</v>
+        <v>6418181</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122508626</v>
+        <v>122508654</v>
       </c>
       <c r="B8" t="n">
         <v>98244</v>
@@ -1392,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581228</v>
+        <v>581242</v>
       </c>
       <c r="R8" t="n">
-        <v>6418409</v>
+        <v>6418411</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122508679</v>
+        <v>122508731</v>
       </c>
       <c r="B9" t="n">
         <v>98244</v>
@@ -1503,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581209</v>
+        <v>581212</v>
       </c>
       <c r="R9" t="n">
-        <v>6418354</v>
+        <v>6418405</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122508578</v>
+        <v>122508509</v>
       </c>
       <c r="B10" t="n">
-        <v>98244</v>
+        <v>57754</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,35 +1575,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1614,13 +1615,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581224</v>
+        <v>581279</v>
       </c>
       <c r="R10" t="n">
-        <v>6418372</v>
+        <v>6418360</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1658,7 +1659,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122510535</v>
+        <v>122508687</v>
       </c>
       <c r="B11" t="n">
         <v>98244</v>
@@ -1710,11 +1710,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1729,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581276</v>
+        <v>581196</v>
       </c>
       <c r="R11" t="n">
-        <v>6418168</v>
+        <v>6418358</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1903,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122510543</v>
+        <v>122508709</v>
       </c>
       <c r="B13" t="n">
-        <v>57537</v>
+        <v>98244</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,39 +1911,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1955,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581276</v>
+        <v>581196</v>
       </c>
       <c r="R13" t="n">
-        <v>6418168</v>
+        <v>6418384</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,6 +1991,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2017,7 +2010,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122510457</v>
+        <v>122510520</v>
       </c>
       <c r="B14" t="n">
         <v>98244</v>
@@ -2065,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581311</v>
+        <v>581270</v>
       </c>
       <c r="R14" t="n">
-        <v>6418384</v>
+        <v>6418180</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122508687</v>
+        <v>122508561</v>
       </c>
       <c r="B15" t="n">
         <v>98244</v>
@@ -2176,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581196</v>
+        <v>581217</v>
       </c>
       <c r="R15" t="n">
-        <v>6418358</v>
+        <v>6418390</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122508731</v>
+        <v>122510446</v>
       </c>
       <c r="B16" t="n">
         <v>98244</v>
@@ -2287,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581212</v>
+        <v>581296</v>
       </c>
       <c r="R16" t="n">
-        <v>6418405</v>
+        <v>6418371</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122508709</v>
+        <v>122510543</v>
       </c>
       <c r="B17" t="n">
-        <v>98244</v>
+        <v>57537</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2362,35 +2355,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2398,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581196</v>
+        <v>581276</v>
       </c>
       <c r="R17" t="n">
-        <v>6418384</v>
+        <v>6418168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,7 +2439,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2461,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122508745</v>
+        <v>122508578</v>
       </c>
       <c r="B18" t="n">
         <v>98244</v>
@@ -2509,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581213</v>
+        <v>581224</v>
       </c>
       <c r="R18" t="n">
-        <v>6418385</v>
+        <v>6418372</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2572,7 +2568,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122508664</v>
+        <v>122508528</v>
       </c>
       <c r="B19" t="n">
         <v>98244</v>
@@ -2620,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581212</v>
+        <v>581231</v>
       </c>
       <c r="R19" t="n">
-        <v>6418357</v>
+        <v>6418384</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,7 +2679,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122508528</v>
+        <v>122510535</v>
       </c>
       <c r="B20" t="n">
         <v>98244</v>
@@ -2716,7 +2712,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581231</v>
+        <v>581276</v>
       </c>
       <c r="R20" t="n">
-        <v>6418384</v>
+        <v>6418168</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2794,7 +2794,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122508561</v>
+        <v>122508619</v>
       </c>
       <c r="B21" t="n">
         <v>98244</v>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581217</v>
+        <v>581220</v>
       </c>
       <c r="R21" t="n">
-        <v>6418390</v>
+        <v>6418393</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,7 +2905,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122508717</v>
+        <v>122508626</v>
       </c>
       <c r="B22" t="n">
         <v>98244</v>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581193</v>
+        <v>581228</v>
       </c>
       <c r="R22" t="n">
-        <v>6418402</v>
+        <v>6418409</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,7 +3016,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122508654</v>
+        <v>122508745</v>
       </c>
       <c r="B23" t="n">
         <v>98244</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581242</v>
+        <v>581213</v>
       </c>
       <c r="R23" t="n">
-        <v>6418411</v>
+        <v>6418385</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 7832-2025 artfynd.xlsx
+++ b/artfynd/A 7832-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122508679</v>
+        <v>122508664</v>
       </c>
       <c r="B2" t="n">
         <v>98244</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581209</v>
+        <v>581212</v>
       </c>
       <c r="R2" t="n">
-        <v>6418354</v>
+        <v>6418357</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122508664</v>
+        <v>122508679</v>
       </c>
       <c r="B3" t="n">
         <v>98244</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581212</v>
+        <v>581209</v>
       </c>
       <c r="R3" t="n">
-        <v>6418357</v>
+        <v>6418354</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 7832-2025 artfynd.xlsx
+++ b/artfynd/A 7832-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122508664</v>
+        <v>122508679</v>
       </c>
       <c r="B2" t="n">
         <v>98244</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581212</v>
+        <v>581209</v>
       </c>
       <c r="R2" t="n">
-        <v>6418357</v>
+        <v>6418354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122508679</v>
+        <v>122508664</v>
       </c>
       <c r="B3" t="n">
         <v>98244</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581209</v>
+        <v>581212</v>
       </c>
       <c r="R3" t="n">
-        <v>6418354</v>
+        <v>6418357</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 7832-2025 artfynd.xlsx
+++ b/artfynd/A 7832-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122508679</v>
+        <v>122508509</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>57848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581209</v>
+        <v>581279</v>
       </c>
       <c r="R2" t="n">
-        <v>6418354</v>
+        <v>6418360</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122508664</v>
+        <v>122508717</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581212</v>
+        <v>581193</v>
       </c>
       <c r="R3" t="n">
-        <v>6418357</v>
+        <v>6418402</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122508717</v>
+        <v>122508679</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581193</v>
+        <v>581209</v>
       </c>
       <c r="R4" t="n">
-        <v>6418402</v>
+        <v>6418354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122508596</v>
+        <v>122510520</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581225</v>
+        <v>581270</v>
       </c>
       <c r="R5" t="n">
-        <v>6418386</v>
+        <v>6418180</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122510457</v>
+        <v>122508578</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581311</v>
+        <v>581224</v>
       </c>
       <c r="R6" t="n">
-        <v>6418384</v>
+        <v>6418372</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122510530</v>
+        <v>122508687</v>
       </c>
       <c r="B7" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581277</v>
+        <v>581196</v>
       </c>
       <c r="R7" t="n">
-        <v>6418181</v>
+        <v>6418358</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122508654</v>
+        <v>122508664</v>
       </c>
       <c r="B8" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581242</v>
+        <v>581212</v>
       </c>
       <c r="R8" t="n">
-        <v>6418411</v>
+        <v>6418357</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122508731</v>
+        <v>122508709</v>
       </c>
       <c r="B9" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581212</v>
+        <v>581196</v>
       </c>
       <c r="R9" t="n">
-        <v>6418405</v>
+        <v>6418384</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122508509</v>
+        <v>122510475</v>
       </c>
       <c r="B10" t="n">
-        <v>57754</v>
+        <v>98347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,39 +1578,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1615,13 +1614,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581279</v>
+        <v>581315</v>
       </c>
       <c r="R10" t="n">
-        <v>6418360</v>
+        <v>6418387</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,6 +1658,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122508687</v>
+        <v>122510457</v>
       </c>
       <c r="B11" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581196</v>
+        <v>581311</v>
       </c>
       <c r="R11" t="n">
-        <v>6418358</v>
+        <v>6418384</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122510475</v>
+        <v>122508626</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581315</v>
+        <v>581228</v>
       </c>
       <c r="R12" t="n">
-        <v>6418387</v>
+        <v>6418409</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122508709</v>
+        <v>122508745</v>
       </c>
       <c r="B13" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581196</v>
+        <v>581213</v>
       </c>
       <c r="R13" t="n">
-        <v>6418384</v>
+        <v>6418385</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122510520</v>
+        <v>122508654</v>
       </c>
       <c r="B14" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581270</v>
+        <v>581242</v>
       </c>
       <c r="R14" t="n">
-        <v>6418180</v>
+        <v>6418411</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122508561</v>
+        <v>122508528</v>
       </c>
       <c r="B15" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581217</v>
+        <v>581231</v>
       </c>
       <c r="R15" t="n">
-        <v>6418390</v>
+        <v>6418384</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122510446</v>
+        <v>122508619</v>
       </c>
       <c r="B16" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581296</v>
+        <v>581220</v>
       </c>
       <c r="R16" t="n">
-        <v>6418371</v>
+        <v>6418393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2346,7 @@
         <v>122510543</v>
       </c>
       <c r="B17" t="n">
-        <v>57537</v>
+        <v>57631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122508578</v>
+        <v>122508596</v>
       </c>
       <c r="B18" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581224</v>
+        <v>581225</v>
       </c>
       <c r="R18" t="n">
-        <v>6418372</v>
+        <v>6418386</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122508528</v>
+        <v>122510530</v>
       </c>
       <c r="B19" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581231</v>
+        <v>581277</v>
       </c>
       <c r="R19" t="n">
-        <v>6418384</v>
+        <v>6418181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2682,7 +2682,7 @@
         <v>122510535</v>
       </c>
       <c r="B20" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122508619</v>
+        <v>122510446</v>
       </c>
       <c r="B21" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581220</v>
+        <v>581296</v>
       </c>
       <c r="R21" t="n">
-        <v>6418393</v>
+        <v>6418371</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,10 +2905,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122508626</v>
+        <v>122508731</v>
       </c>
       <c r="B22" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581228</v>
+        <v>581212</v>
       </c>
       <c r="R22" t="n">
-        <v>6418409</v>
+        <v>6418405</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122508745</v>
+        <v>122508561</v>
       </c>
       <c r="B23" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581213</v>
+        <v>581217</v>
       </c>
       <c r="R23" t="n">
-        <v>6418385</v>
+        <v>6418390</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3130,7 +3130,7 @@
         <v>122667735</v>
       </c>
       <c r="B24" t="n">
-        <v>57537</v>
+        <v>57631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 7832-2025 artfynd.xlsx
+++ b/artfynd/A 7832-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122508509</v>
+        <v>122510475</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581279</v>
+        <v>581315</v>
       </c>
       <c r="R2" t="n">
-        <v>6418360</v>
+        <v>6418387</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,7 +789,7 @@
         <v>122508717</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122508679</v>
+        <v>122508745</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581209</v>
+        <v>581213</v>
       </c>
       <c r="R4" t="n">
-        <v>6418354</v>
+        <v>6418385</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122510520</v>
+        <v>122508578</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581270</v>
+        <v>581224</v>
       </c>
       <c r="R5" t="n">
-        <v>6418180</v>
+        <v>6418372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122508578</v>
+        <v>122508561</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581224</v>
+        <v>581217</v>
       </c>
       <c r="R6" t="n">
-        <v>6418372</v>
+        <v>6418390</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122508687</v>
+        <v>122508679</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581196</v>
+        <v>581209</v>
       </c>
       <c r="R7" t="n">
-        <v>6418358</v>
+        <v>6418354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122508664</v>
+        <v>122510543</v>
       </c>
       <c r="B8" t="n">
-        <v>98347</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,35 +1353,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581212</v>
+        <v>581276</v>
       </c>
       <c r="R8" t="n">
-        <v>6418357</v>
+        <v>6418168</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1437,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122508709</v>
+        <v>122508509</v>
       </c>
       <c r="B9" t="n">
-        <v>98347</v>
+        <v>57848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,35 +1467,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,13 +1507,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581196</v>
+        <v>581279</v>
       </c>
       <c r="R9" t="n">
-        <v>6418384</v>
+        <v>6418360</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1551,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1566,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122510475</v>
+        <v>122508664</v>
       </c>
       <c r="B10" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581315</v>
+        <v>581212</v>
       </c>
       <c r="R10" t="n">
-        <v>6418387</v>
+        <v>6418357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122510457</v>
+        <v>122508626</v>
       </c>
       <c r="B11" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581311</v>
+        <v>581228</v>
       </c>
       <c r="R11" t="n">
-        <v>6418384</v>
+        <v>6418409</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122508626</v>
+        <v>122508619</v>
       </c>
       <c r="B12" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581228</v>
+        <v>581220</v>
       </c>
       <c r="R12" t="n">
-        <v>6418409</v>
+        <v>6418393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122508745</v>
+        <v>122510446</v>
       </c>
       <c r="B13" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581213</v>
+        <v>581296</v>
       </c>
       <c r="R13" t="n">
-        <v>6418385</v>
+        <v>6418371</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122508654</v>
+        <v>122510530</v>
       </c>
       <c r="B14" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581242</v>
+        <v>581277</v>
       </c>
       <c r="R14" t="n">
-        <v>6418411</v>
+        <v>6418181</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122508528</v>
+        <v>122508709</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,7 +2172,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581231</v>
+        <v>581196</v>
       </c>
       <c r="R15" t="n">
         <v>6418384</v>
@@ -2232,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122508619</v>
+        <v>122510535</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2265,7 +2268,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2280,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581220</v>
+        <v>581276</v>
       </c>
       <c r="R16" t="n">
-        <v>6418393</v>
+        <v>6418168</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122510543</v>
+        <v>122508731</v>
       </c>
       <c r="B17" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2355,39 +2362,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2395,10 +2398,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581276</v>
+        <v>581212</v>
       </c>
       <c r="R17" t="n">
-        <v>6418168</v>
+        <v>6418405</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,6 +2442,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2457,10 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122508596</v>
+        <v>122510520</v>
       </c>
       <c r="B18" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581225</v>
+        <v>581270</v>
       </c>
       <c r="R18" t="n">
-        <v>6418386</v>
+        <v>6418180</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,10 +2572,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122510530</v>
+        <v>122508528</v>
       </c>
       <c r="B19" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2616,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581277</v>
+        <v>581231</v>
       </c>
       <c r="R19" t="n">
-        <v>6418181</v>
+        <v>6418384</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2679,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122510535</v>
+        <v>122508596</v>
       </c>
       <c r="B20" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,11 +2716,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581276</v>
+        <v>581225</v>
       </c>
       <c r="R20" t="n">
-        <v>6418168</v>
+        <v>6418386</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2794,10 +2794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122510446</v>
+        <v>122508654</v>
       </c>
       <c r="B21" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581296</v>
+        <v>581242</v>
       </c>
       <c r="R21" t="n">
-        <v>6418371</v>
+        <v>6418411</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,10 +2905,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122508731</v>
+        <v>122510457</v>
       </c>
       <c r="B22" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581212</v>
+        <v>581311</v>
       </c>
       <c r="R22" t="n">
-        <v>6418405</v>
+        <v>6418384</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122508561</v>
+        <v>122508687</v>
       </c>
       <c r="B23" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581217</v>
+        <v>581196</v>
       </c>
       <c r="R23" t="n">
-        <v>6418390</v>
+        <v>6418358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 7832-2025 artfynd.xlsx
+++ b/artfynd/A 7832-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122510475</v>
+        <v>122510530</v>
       </c>
       <c r="B2" t="n">
         <v>98355</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581315</v>
+        <v>581277</v>
       </c>
       <c r="R2" t="n">
-        <v>6418387</v>
+        <v>6418181</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122508717</v>
+        <v>122510520</v>
       </c>
       <c r="B3" t="n">
         <v>98355</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581193</v>
+        <v>581270</v>
       </c>
       <c r="R3" t="n">
-        <v>6418402</v>
+        <v>6418180</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122508745</v>
+        <v>122510446</v>
       </c>
       <c r="B4" t="n">
         <v>98355</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581213</v>
+        <v>581296</v>
       </c>
       <c r="R4" t="n">
-        <v>6418385</v>
+        <v>6418371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122508578</v>
+        <v>122508626</v>
       </c>
       <c r="B5" t="n">
         <v>98355</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581224</v>
+        <v>581228</v>
       </c>
       <c r="R5" t="n">
-        <v>6418372</v>
+        <v>6418409</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122508561</v>
+        <v>122508731</v>
       </c>
       <c r="B6" t="n">
         <v>98355</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581217</v>
+        <v>581212</v>
       </c>
       <c r="R6" t="n">
-        <v>6418390</v>
+        <v>6418405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122508679</v>
+        <v>122508717</v>
       </c>
       <c r="B7" t="n">
         <v>98355</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581209</v>
+        <v>581193</v>
       </c>
       <c r="R7" t="n">
-        <v>6418354</v>
+        <v>6418402</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122510543</v>
+        <v>122510475</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,39 +1353,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581276</v>
+        <v>581315</v>
       </c>
       <c r="R8" t="n">
-        <v>6418168</v>
+        <v>6418387</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,6 +1433,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122508509</v>
+        <v>122508578</v>
       </c>
       <c r="B9" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,39 +1464,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581279</v>
+        <v>581224</v>
       </c>
       <c r="R9" t="n">
-        <v>6418360</v>
+        <v>6418372</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,6 +1544,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1680,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122508626</v>
+        <v>122508528</v>
       </c>
       <c r="B11" t="n">
         <v>98355</v>
@@ -1728,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581228</v>
+        <v>581231</v>
       </c>
       <c r="R11" t="n">
-        <v>6418409</v>
+        <v>6418384</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122508619</v>
+        <v>122508561</v>
       </c>
       <c r="B12" t="n">
         <v>98355</v>
@@ -1839,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581220</v>
+        <v>581217</v>
       </c>
       <c r="R12" t="n">
-        <v>6418393</v>
+        <v>6418390</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122510446</v>
+        <v>122510535</v>
       </c>
       <c r="B13" t="n">
         <v>98355</v>
@@ -1935,7 +1929,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1950,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581296</v>
+        <v>581276</v>
       </c>
       <c r="R13" t="n">
-        <v>6418371</v>
+        <v>6418168</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2011,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122510530</v>
+        <v>122508619</v>
       </c>
       <c r="B14" t="n">
         <v>98355</v>
@@ -2061,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581277</v>
+        <v>581220</v>
       </c>
       <c r="R14" t="n">
-        <v>6418181</v>
+        <v>6418393</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2122,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122508709</v>
+        <v>122508654</v>
       </c>
       <c r="B15" t="n">
         <v>98355</v>
@@ -2172,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581196</v>
+        <v>581242</v>
       </c>
       <c r="R15" t="n">
-        <v>6418384</v>
+        <v>6418411</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2233,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122510535</v>
+        <v>122508596</v>
       </c>
       <c r="B16" t="n">
         <v>98355</v>
@@ -2268,11 +2266,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2287,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581276</v>
+        <v>581225</v>
       </c>
       <c r="R16" t="n">
-        <v>6418168</v>
+        <v>6418386</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,7 +2344,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122508731</v>
+        <v>122510457</v>
       </c>
       <c r="B17" t="n">
         <v>98355</v>
@@ -2398,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581212</v>
+        <v>581311</v>
       </c>
       <c r="R17" t="n">
-        <v>6418405</v>
+        <v>6418384</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2455,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122510520</v>
+        <v>122508709</v>
       </c>
       <c r="B18" t="n">
         <v>98355</v>
@@ -2509,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581270</v>
+        <v>581196</v>
       </c>
       <c r="R18" t="n">
-        <v>6418180</v>
+        <v>6418384</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2572,7 +2566,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122508528</v>
+        <v>122508687</v>
       </c>
       <c r="B19" t="n">
         <v>98355</v>
@@ -2620,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581231</v>
+        <v>581196</v>
       </c>
       <c r="R19" t="n">
-        <v>6418384</v>
+        <v>6418358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,10 +2677,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122508596</v>
+        <v>122508509</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>57848</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2695,35 +2689,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2731,13 +2729,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581225</v>
+        <v>581279</v>
       </c>
       <c r="R20" t="n">
-        <v>6418386</v>
+        <v>6418360</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2775,7 +2773,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2794,7 +2791,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122508654</v>
+        <v>122508745</v>
       </c>
       <c r="B21" t="n">
         <v>98355</v>
@@ -2842,10 +2839,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581242</v>
+        <v>581213</v>
       </c>
       <c r="R21" t="n">
-        <v>6418411</v>
+        <v>6418385</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,7 +2902,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122510457</v>
+        <v>122508679</v>
       </c>
       <c r="B22" t="n">
         <v>98355</v>
@@ -2953,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581311</v>
+        <v>581209</v>
       </c>
       <c r="R22" t="n">
-        <v>6418384</v>
+        <v>6418354</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,10 +3013,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122508687</v>
+        <v>122510543</v>
       </c>
       <c r="B23" t="n">
-        <v>98355</v>
+        <v>57631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3028,35 +3025,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3064,10 +3065,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581196</v>
+        <v>581276</v>
       </c>
       <c r="R23" t="n">
-        <v>6418358</v>
+        <v>6418168</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3108,7 +3109,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7832-2025 artfynd.xlsx
+++ b/artfynd/A 7832-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122510530</v>
+        <v>122510446</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581277</v>
+        <v>581296</v>
       </c>
       <c r="R2" t="n">
-        <v>6418181</v>
+        <v>6418371</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122510520</v>
+        <v>122508731</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581270</v>
+        <v>581212</v>
       </c>
       <c r="R3" t="n">
-        <v>6418180</v>
+        <v>6418405</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122510446</v>
+        <v>122508596</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581296</v>
+        <v>581225</v>
       </c>
       <c r="R4" t="n">
-        <v>6418371</v>
+        <v>6418386</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122508626</v>
+        <v>122508679</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581228</v>
+        <v>581209</v>
       </c>
       <c r="R5" t="n">
-        <v>6418409</v>
+        <v>6418354</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122508731</v>
+        <v>122508509</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,35 +1131,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581212</v>
+        <v>581279</v>
       </c>
       <c r="R6" t="n">
-        <v>6418405</v>
+        <v>6418360</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1215,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122508717</v>
+        <v>122508709</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581193</v>
+        <v>581196</v>
       </c>
       <c r="R7" t="n">
-        <v>6418402</v>
+        <v>6418384</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122510475</v>
+        <v>122510535</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,7 +1377,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1389,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581315</v>
+        <v>581276</v>
       </c>
       <c r="R8" t="n">
-        <v>6418387</v>
+        <v>6418168</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122508578</v>
+        <v>122510520</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581224</v>
+        <v>581270</v>
       </c>
       <c r="R9" t="n">
-        <v>6418372</v>
+        <v>6418180</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122508664</v>
+        <v>122508626</v>
       </c>
       <c r="B10" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581212</v>
+        <v>581228</v>
       </c>
       <c r="R10" t="n">
-        <v>6418357</v>
+        <v>6418409</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1684,7 @@
         <v>122508528</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122508561</v>
+        <v>122508654</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581217</v>
+        <v>581242</v>
       </c>
       <c r="R12" t="n">
-        <v>6418390</v>
+        <v>6418411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122510535</v>
+        <v>122508578</v>
       </c>
       <c r="B13" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,11 +1936,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1948,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581276</v>
+        <v>581224</v>
       </c>
       <c r="R13" t="n">
-        <v>6418168</v>
+        <v>6418372</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122508619</v>
+        <v>122508745</v>
       </c>
       <c r="B14" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581220</v>
+        <v>581213</v>
       </c>
       <c r="R14" t="n">
-        <v>6418393</v>
+        <v>6418385</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122508654</v>
+        <v>122510457</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581242</v>
+        <v>581311</v>
       </c>
       <c r="R15" t="n">
-        <v>6418411</v>
+        <v>6418384</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122508596</v>
+        <v>122508687</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581225</v>
+        <v>581196</v>
       </c>
       <c r="R16" t="n">
-        <v>6418386</v>
+        <v>6418358</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122510457</v>
+        <v>122510543</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>57631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,35 +2359,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2392,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581311</v>
+        <v>581276</v>
       </c>
       <c r="R17" t="n">
-        <v>6418384</v>
+        <v>6418168</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2436,7 +2443,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2455,10 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122508709</v>
+        <v>122508561</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581196</v>
+        <v>581217</v>
       </c>
       <c r="R18" t="n">
-        <v>6418384</v>
+        <v>6418390</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,10 +2572,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122508687</v>
+        <v>122508619</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2614,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581196</v>
+        <v>581220</v>
       </c>
       <c r="R19" t="n">
-        <v>6418358</v>
+        <v>6418393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2677,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122508509</v>
+        <v>122510475</v>
       </c>
       <c r="B20" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2689,39 +2695,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2729,13 +2731,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581279</v>
+        <v>581315</v>
       </c>
       <c r="R20" t="n">
-        <v>6418360</v>
+        <v>6418387</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2773,6 +2775,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2791,10 +2794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122508745</v>
+        <v>122508717</v>
       </c>
       <c r="B21" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581213</v>
+        <v>581193</v>
       </c>
       <c r="R21" t="n">
-        <v>6418385</v>
+        <v>6418402</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2902,10 +2905,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122508679</v>
+        <v>122508664</v>
       </c>
       <c r="B22" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2950,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581209</v>
+        <v>581212</v>
       </c>
       <c r="R22" t="n">
-        <v>6418354</v>
+        <v>6418357</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3013,10 +3016,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122510543</v>
+        <v>122510530</v>
       </c>
       <c r="B23" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3025,39 +3028,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3065,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581276</v>
+        <v>581277</v>
       </c>
       <c r="R23" t="n">
-        <v>6418168</v>
+        <v>6418181</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3109,6 +3108,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7832-2025 artfynd.xlsx
+++ b/artfynd/A 7832-2025 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122508596</v>
+        <v>122508509</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +909,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581225</v>
+        <v>581279</v>
       </c>
       <c r="R4" t="n">
-        <v>6418386</v>
+        <v>6418360</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +993,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1008,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122508679</v>
+        <v>122508596</v>
       </c>
       <c r="B5" t="n">
         <v>98357</v>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581209</v>
+        <v>581225</v>
       </c>
       <c r="R5" t="n">
-        <v>6418354</v>
+        <v>6418386</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122508509</v>
+        <v>122508679</v>
       </c>
       <c r="B6" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,39 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581279</v>
+        <v>581209</v>
       </c>
       <c r="R6" t="n">
-        <v>6418360</v>
+        <v>6418354</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,6 +1214,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7832-2025 artfynd.xlsx
+++ b/artfynd/A 7832-2025 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122508509</v>
+        <v>122508596</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,39 +909,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581279</v>
+        <v>581225</v>
       </c>
       <c r="R4" t="n">
-        <v>6418360</v>
+        <v>6418386</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,6 +989,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122508596</v>
+        <v>122508679</v>
       </c>
       <c r="B5" t="n">
         <v>98357</v>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581225</v>
+        <v>581209</v>
       </c>
       <c r="R5" t="n">
-        <v>6418386</v>
+        <v>6418354</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122508679</v>
+        <v>122508509</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1131,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581209</v>
+        <v>581279</v>
       </c>
       <c r="R6" t="n">
-        <v>6418354</v>
+        <v>6418360</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1215,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
